--- a/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
+++ b/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at UTC</t>
   </si>
   <si>
-    <t>2026-05-09T19:56:56.856717+00:00</t>
+    <t>2026-05-09T20:32:56.535581+00:00</t>
   </si>
   <si>
     <t>Data status</t>
@@ -595,151 +595,151 @@
     <t>suggested_action</t>
   </si>
   <si>
-    <t>2026-05-09 19:56:54.872326+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:54.901566+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:54.924245+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:54.955486+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:54.987658+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.012297+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.030211+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.055647+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.073418+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.094092+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.137166+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.162443+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.182035+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.206597+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.224074+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.242234+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.257678+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.276163+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.299966+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.324158+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.341158+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.354817+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.367830+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.385535+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.440566+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.467528+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.489635+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.520642+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.546610+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.570473+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.588130+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.613581+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.634541+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.658960+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.682695+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.708016+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.727506+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.752034+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.770381+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.788415+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.805531+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.823274+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.846934+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.870582+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.887596+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.904743+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.920455+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:55.944659+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 19:56:56.084564+00:00</t>
+    <t>2026-05-09 20:32:54.902658+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:54.930146+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:54.952639+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:54.983582+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.010013+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.033994+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.051632+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.076897+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.094883+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.114945+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.137884+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.162872+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.182069+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.206143+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.223776+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.241574+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.257094+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.274926+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.298487+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.322554+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.339391+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.352197+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.365220+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.403804+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.453307+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.479544+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.501055+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.532169+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.558667+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.582391+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.600220+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.625581+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.643438+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.663707+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.687055+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.712072+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.731415+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.755594+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.773173+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.791205+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.807002+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.824901+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.848713+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.872504+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.889299+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.902165+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.915182+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:55.932609+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-09 20:32:56.054869+00:00</t>
   </si>
   <si>
     <t>low</t>
@@ -1327,7 +1327,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>2026-05-09T19:56:49.517408+00:00</t>
+    <t>2026-05-09T20:32:50.212572+00:00</t>
   </si>
   <si>
     <t>synthetic scenario: base</t>

--- a/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
+++ b/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at UTC</t>
   </si>
   <si>
-    <t>2026-05-09T20:54:09.770943+00:00</t>
+    <t>2026-05-11T10:28:05.432717+00:00</t>
   </si>
   <si>
     <t>Data status</t>
@@ -598,151 +598,151 @@
     <t>suggested_action</t>
   </si>
   <si>
-    <t>2026-05-09 20:52:30.040438+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.075068+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.100820+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.137821+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.168855+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.197483+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.218434+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.248229+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.268641+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.293580+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.319058+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.349265+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.372985+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.411307+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.432030+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.451096+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.468748+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.502835+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.530567+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.557912+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.577139+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.595534+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.612622+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.633079+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.700001+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.732008+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.757702+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.793743+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.823934+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.849992+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.870246+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.901274+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.923791+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.946577+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:30.973914+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:31.001304+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:31.024344+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:31.049802+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:31.069780+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:31.091357+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:31.108942+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:31.129038+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:31.156960+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:31.183276+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:31.206799+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:31.221371+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:31.235870+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:31.257589+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-09 20:52:31.417715+00:00</t>
+    <t>2026-05-11 10:28:03.595592+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:03.623890+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:03.646980+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:03.678734+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:03.706182+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:03.730892+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:03.748963+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:03.775435+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:03.793856+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:03.814802+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:03.838431+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:03.864442+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:03.884180+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:03.908997+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:03.926923+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:03.945168+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:03.961168+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:03.979376+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.003514+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.028241+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.045565+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.058752+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.072300+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.116907+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.167764+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.194772+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.216942+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.248827+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.275946+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.300577+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.319109+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.345179+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.363717+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.384531+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.408246+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.434056+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.454009+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.483688+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.505993+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.526820+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.543045+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.562354+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.586659+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.611337+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.630548+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.644145+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.657389+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.676677+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 10:28:04.806992+00:00</t>
   </si>
   <si>
     <t>low</t>
@@ -1330,7 +1330,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>2026-05-09T20:52:22.782289+00:00</t>
+    <t>2026-05-11T10:27:58.255868+00:00</t>
   </si>
   <si>
     <t>synthetic scenario: base</t>

--- a/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
+++ b/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at UTC</t>
   </si>
   <si>
-    <t>2026-05-11T10:28:05.432717+00:00</t>
+    <t>2026-05-18T10:56:37.784007+00:00</t>
   </si>
   <si>
     <t>Data status</t>
@@ -598,151 +598,151 @@
     <t>suggested_action</t>
   </si>
   <si>
-    <t>2026-05-11 10:28:03.595592+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:03.623890+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:03.646980+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:03.678734+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:03.706182+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:03.730892+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:03.748963+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:03.775435+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:03.793856+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:03.814802+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:03.838431+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:03.864442+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:03.884180+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:03.908997+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:03.926923+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:03.945168+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:03.961168+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:03.979376+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.003514+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.028241+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.045565+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.058752+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.072300+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.116907+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.167764+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.194772+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.216942+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.248827+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.275946+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.300577+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.319109+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.345179+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.363717+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.384531+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.408246+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.434056+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.454009+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.483688+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.505993+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.526820+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.543045+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.562354+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.586659+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.611337+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.630548+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.644145+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.657389+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.676677+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-11 10:28:04.806992+00:00</t>
+    <t>2026-05-18 10:56:35.980468+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.011456+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.036041+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.070485+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.099623+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.126143+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.145624+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.173527+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.193450+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.215900+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.241192+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.268802+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.289973+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.316485+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.336030+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.355962+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.373485+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.393488+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.419401+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.445801+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.464328+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.478649+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.493208+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.534827+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.590904+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.619999+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.643814+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.678162+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.707559+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.734475+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.754587+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.782876+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.802859+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.825295+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.850879+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.878907+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.900159+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.927105+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.946833+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.966713+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:36.984498+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:37.004251+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:37.031035+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:37.058238+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:37.077997+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:37.092569+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:37.107138+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:37.127081+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-18 10:56:37.268489+00:00</t>
   </si>
   <si>
     <t>low</t>
@@ -1330,7 +1330,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>2026-05-11T10:27:58.255868+00:00</t>
+    <t>2026-05-18T10:56:30.429417+00:00</t>
   </si>
   <si>
     <t>synthetic scenario: base</t>

--- a/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
+++ b/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at UTC</t>
   </si>
   <si>
-    <t>2026-05-18T10:56:37.784007+00:00</t>
+    <t>2026-05-25T11:04:08.690859+00:00</t>
   </si>
   <si>
     <t>Data status</t>
@@ -598,151 +598,151 @@
     <t>suggested_action</t>
   </si>
   <si>
-    <t>2026-05-18 10:56:35.980468+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.011456+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.036041+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.070485+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.099623+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.126143+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.145624+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.173527+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.193450+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.215900+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.241192+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.268802+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.289973+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.316485+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.336030+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.355962+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.373485+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.393488+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.419401+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.445801+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.464328+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.478649+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.493208+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.534827+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.590904+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.619999+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.643814+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.678162+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.707559+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.734475+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.754587+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.782876+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.802859+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.825295+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.850879+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.878907+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.900159+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.927105+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.946833+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.966713+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:36.984498+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:37.004251+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:37.031035+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:37.058238+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:37.077997+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:37.092569+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:37.107138+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:37.127081+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-18 10:56:37.268489+00:00</t>
+    <t>2026-05-25 11:04:06.960887+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:06.989963+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.013269+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.045208+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.072529+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.097237+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.115557+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.141953+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.160602+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.181791+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.205722+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.232000+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.251888+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.277226+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.295508+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.314109+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.330249+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.349194+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.373743+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.398694+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.416107+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.429408+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.442951+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.488862+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.539918+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.567048+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.589221+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.621848+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.649367+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.674281+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.692963+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.719210+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.737955+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.759028+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.783107+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.808932+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.828792+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.853990+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.872367+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.890939+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.907779+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.926588+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.951371+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.976672+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:07.994261+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:08.007828+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:08.021367+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:08.039509+00:00</t>
+  </si>
+  <si>
+    <t>2026-05-25 11:04:08.168251+00:00</t>
   </si>
   <si>
     <t>low</t>
@@ -1330,7 +1330,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>2026-05-18T10:56:30.429417+00:00</t>
+    <t>2026-05-25T11:04:01.651512+00:00</t>
   </si>
   <si>
     <t>synthetic scenario: base</t>

--- a/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
+++ b/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at UTC</t>
   </si>
   <si>
-    <t>2026-05-25T11:04:08.690859+00:00</t>
+    <t>2026-06-01T12:28:50.933444+00:00</t>
   </si>
   <si>
     <t>Data status</t>
@@ -598,151 +598,151 @@
     <t>suggested_action</t>
   </si>
   <si>
-    <t>2026-05-25 11:04:06.960887+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:06.989963+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.013269+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.045208+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.072529+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.097237+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.115557+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.141953+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.160602+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.181791+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.205722+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.232000+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.251888+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.277226+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.295508+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.314109+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.330249+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.349194+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.373743+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.398694+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.416107+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.429408+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.442951+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.488862+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.539918+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.567048+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.589221+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.621848+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.649367+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.674281+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.692963+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.719210+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.737955+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.759028+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.783107+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.808932+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.828792+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.853990+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.872367+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.890939+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.907779+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.926588+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.951371+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.976672+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:07.994261+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:08.007828+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:08.021367+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:08.039509+00:00</t>
-  </si>
-  <si>
-    <t>2026-05-25 11:04:08.168251+00:00</t>
+    <t>2026-06-01 12:28:48.978828+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.008551+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.032037+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.064185+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.091797+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.116754+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.135143+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.161550+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.180247+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.201057+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.224821+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.250836+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.270694+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.295680+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.314189+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.333305+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.349590+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.368146+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.392728+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.419168+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.436657+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.449870+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.463540+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.511260+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.562561+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.589943+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.612123+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.644086+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.671744+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.696525+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.715007+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.741628+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.761227+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.782109+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.806900+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.833080+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.853276+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.882146+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.909196+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.931452+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.948098+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.966929+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:49.991724+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:50.017258+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:50.041441+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:50.055281+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:50.070611+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:50.098769+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:28:50.265867+00:00</t>
   </si>
   <si>
     <t>low</t>
@@ -1330,7 +1330,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>2026-05-25T11:04:01.651512+00:00</t>
+    <t>2026-06-01T12:28:43.797079+00:00</t>
   </si>
   <si>
     <t>synthetic scenario: base</t>

--- a/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
+++ b/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at UTC</t>
   </si>
   <si>
-    <t>2026-06-01T12:28:50.933444+00:00</t>
+    <t>2026-06-08T11:48:48.332186+00:00</t>
   </si>
   <si>
     <t>Data status</t>
@@ -598,151 +598,151 @@
     <t>suggested_action</t>
   </si>
   <si>
-    <t>2026-06-01 12:28:48.978828+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.008551+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.032037+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.064185+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.091797+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.116754+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.135143+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.161550+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.180247+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.201057+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.224821+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.250836+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.270694+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.295680+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.314189+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.333305+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.349590+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.368146+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.392728+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.419168+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.436657+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.449870+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.463540+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.511260+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.562561+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.589943+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.612123+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.644086+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.671744+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.696525+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.715007+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.741628+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.761227+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.782109+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.806900+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.833080+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.853276+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.882146+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.909196+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.931452+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.948098+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.966929+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:49.991724+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:50.017258+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:50.041441+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:50.055281+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:50.070611+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:50.098769+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:28:50.265867+00:00</t>
+    <t>2026-06-08 11:48:46.471894+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:46.504133+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:46.529244+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:46.563894+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:46.593578+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:46.620779+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:46.640802+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:46.669345+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:46.689573+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:46.712287+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:46.738178+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:46.766295+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:46.787817+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:46.815215+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:46.835158+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:46.855456+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:46.873236+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:46.893743+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:46.920532+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:46.947810+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:46.967062+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:46.981632+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:46.996430+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.039662+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.095972+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.125968+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.150308+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.185231+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.215092+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.242387+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.262885+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.291775+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.312377+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.335202+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.361558+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.390091+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.412163+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.440486+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.460948+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.481651+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.500019+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.520787+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.548336+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.576269+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.595797+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.610906+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.625804+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.645681+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 11:48:47.790314+00:00</t>
   </si>
   <si>
     <t>low</t>
@@ -1330,7 +1330,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>2026-06-01T12:28:43.797079+00:00</t>
+    <t>2026-06-08T11:48:40.031899+00:00</t>
   </si>
   <si>
     <t>synthetic scenario: base</t>

--- a/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
+++ b/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at UTC</t>
   </si>
   <si>
-    <t>2026-06-08T11:48:48.332186+00:00</t>
+    <t>2026-06-15T12:56:52.899180+00:00</t>
   </si>
   <si>
     <t>Data status</t>
@@ -598,151 +598,151 @@
     <t>suggested_action</t>
   </si>
   <si>
-    <t>2026-06-08 11:48:46.471894+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:46.504133+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:46.529244+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:46.563894+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:46.593578+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:46.620779+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:46.640802+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:46.669345+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:46.689573+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:46.712287+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:46.738178+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:46.766295+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:46.787817+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:46.815215+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:46.835158+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:46.855456+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:46.873236+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:46.893743+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:46.920532+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:46.947810+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:46.967062+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:46.981632+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:46.996430+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.039662+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.095972+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.125968+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.150308+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.185231+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.215092+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.242387+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.262885+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.291775+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.312377+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.335202+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.361558+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.390091+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.412163+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.440486+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.460948+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.481651+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.500019+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.520787+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.548336+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.576269+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.595797+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.610906+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.625804+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.645681+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:48:47.790314+00:00</t>
+    <t>2026-06-15 12:56:51.146325+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.176195+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.199611+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.231840+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.259179+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.283961+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.302099+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.328470+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.347259+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.368226+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.392240+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.418297+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.438080+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.463205+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.481527+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.500188+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.516556+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.535252+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.559850+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.584862+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.602484+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.615799+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.629411+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.687982+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.739459+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.766847+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.789113+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.821295+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.848739+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.873523+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.892061+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.918496+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.937220+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.958273+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:51.982212+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:52.008165+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:52.028315+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:52.053659+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:52.072115+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:52.090617+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:52.107095+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:52.125850+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:52.150601+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:52.175388+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:52.192926+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:52.206295+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:52.219806+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:52.238200+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-15 12:56:52.365563+00:00</t>
   </si>
   <si>
     <t>low</t>
@@ -1330,7 +1330,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>2026-06-08T11:48:40.031899+00:00</t>
+    <t>2026-06-15T12:56:45.711012+00:00</t>
   </si>
   <si>
     <t>synthetic scenario: base</t>

--- a/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
+++ b/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at UTC</t>
   </si>
   <si>
-    <t>2026-06-15T12:56:52.899180+00:00</t>
+    <t>2026-06-22T12:42:04.985516+00:00</t>
   </si>
   <si>
     <t>Data status</t>
@@ -598,151 +598,151 @@
     <t>suggested_action</t>
   </si>
   <si>
-    <t>2026-06-15 12:56:51.146325+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.176195+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.199611+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.231840+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.259179+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.283961+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.302099+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.328470+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.347259+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.368226+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.392240+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.418297+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.438080+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.463205+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.481527+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.500188+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.516556+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.535252+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.559850+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.584862+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.602484+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.615799+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.629411+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.687982+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.739459+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.766847+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.789113+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.821295+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.848739+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.873523+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.892061+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.918496+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.937220+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.958273+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:51.982212+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:52.008165+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:52.028315+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:52.053659+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:52.072115+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:52.090617+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:52.107095+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:52.125850+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:52.150601+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:52.175388+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:52.192926+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:52.206295+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:52.219806+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:52.238200+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:56:52.365563+00:00</t>
+    <t>2026-06-22 12:42:03.322871+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.351779+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.374283+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.405491+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.432502+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.456531+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.474325+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.500449+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.518975+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.539384+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.562566+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.588124+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.607543+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.631872+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.649802+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.668137+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.684083+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.702410+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.726149+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.750778+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.768321+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.781241+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.794354+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.832181+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.882516+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.909020+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.930947+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.962232+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:03.988978+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:04.013315+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:04.031706+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:04.057444+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:04.075629+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:04.096390+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:04.119730+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:04.145816+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:04.168150+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:04.193987+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:04.216348+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:04.237983+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:04.254402+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:04.272857+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:04.296926+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:04.321479+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:04.338967+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:04.352441+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:04.365792+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:04.383441+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:42:04.506779+00:00</t>
   </si>
   <si>
     <t>low</t>
@@ -1330,7 +1330,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>2026-06-15T12:56:45.711012+00:00</t>
+    <t>2026-06-22T12:41:58.355818+00:00</t>
   </si>
   <si>
     <t>synthetic scenario: base</t>

--- a/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
+++ b/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at UTC</t>
   </si>
   <si>
-    <t>2026-06-22T12:42:04.985516+00:00</t>
+    <t>2026-06-29T11:52:31.470900+00:00</t>
   </si>
   <si>
     <t>Data status</t>
@@ -598,151 +598,151 @@
     <t>suggested_action</t>
   </si>
   <si>
-    <t>2026-06-22 12:42:03.322871+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.351779+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.374283+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.405491+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.432502+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.456531+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.474325+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.500449+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.518975+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.539384+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.562566+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.588124+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.607543+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.631872+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.649802+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.668137+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.684083+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.702410+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.726149+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.750778+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.768321+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.781241+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.794354+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.832181+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.882516+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.909020+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.930947+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.962232+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:03.988978+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:04.013315+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:04.031706+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:04.057444+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:04.075629+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:04.096390+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:04.119730+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:04.145816+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:04.168150+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:04.193987+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:04.216348+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:04.237983+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:04.254402+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:04.272857+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:04.296926+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:04.321479+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:04.338967+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:04.352441+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:04.365792+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:04.383441+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:42:04.506779+00:00</t>
+    <t>2026-06-29 11:52:29.705546+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:29.737092+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:29.761333+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:29.795811+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:29.825083+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:29.851545+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:29.871016+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:29.899071+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:29.919073+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:29.941431+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:29.966884+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:29.994542+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.015946+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.042877+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.062701+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.082613+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.100359+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.120341+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.146529+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.173179+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.191902+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.206128+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.239357+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.258806+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.313987+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.343156+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.366874+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.400924+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.430060+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.456784+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.476272+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.504291+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.524189+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.546693+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.572102+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.599992+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.621208+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.648911+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.668487+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.688599+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.705944+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.725860+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.752107+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.778766+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.797429+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.811850+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.826261+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.847465+00:00</t>
+  </si>
+  <si>
+    <t>2026-06-29 11:52:30.984122+00:00</t>
   </si>
   <si>
     <t>low</t>
@@ -1330,7 +1330,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>2026-06-22T12:41:58.355818+00:00</t>
+    <t>2026-06-29T11:52:24.359840+00:00</t>
   </si>
   <si>
     <t>synthetic scenario: base</t>

--- a/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
+++ b/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at UTC</t>
   </si>
   <si>
-    <t>2026-06-29T11:52:31.470900+00:00</t>
+    <t>2026-07-06T11:21:23.872004+00:00</t>
   </si>
   <si>
     <t>Data status</t>
@@ -598,151 +598,151 @@
     <t>suggested_action</t>
   </si>
   <si>
-    <t>2026-06-29 11:52:29.705546+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:29.737092+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:29.761333+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:29.795811+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:29.825083+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:29.851545+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:29.871016+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:29.899071+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:29.919073+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:29.941431+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:29.966884+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:29.994542+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.015946+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.042877+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.062701+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.082613+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.100359+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.120341+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.146529+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.173179+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.191902+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.206128+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.239357+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.258806+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.313987+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.343156+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.366874+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.400924+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.430060+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.456784+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.476272+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.504291+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.524189+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.546693+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.572102+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.599992+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.621208+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.648911+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.668487+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.688599+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.705944+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.725860+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.752107+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.778766+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.797429+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.811850+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.826261+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.847465+00:00</t>
-  </si>
-  <si>
-    <t>2026-06-29 11:52:30.984122+00:00</t>
+    <t>2026-07-06 11:21:22.153256+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.184848+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.208285+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.240237+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.269272+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.293515+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.311356+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.337088+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.356460+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.376906+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.400081+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.425359+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.444587+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.469014+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.486900+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.505041+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.520839+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.538886+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.562744+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.587107+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.604201+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.617188+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.631591+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.690560+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.751358+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.779791+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.801858+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.833488+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.860255+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.884933+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.903501+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.929657+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.948082+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.968819+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:22.992454+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:23.018078+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:23.037846+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:23.062602+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:23.080502+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:23.098605+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:23.114728+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:23.132944+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:23.157194+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:23.181475+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:23.198656+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:23.211910+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:23.225249+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:23.242871+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:21:23.368389+00:00</t>
   </si>
   <si>
     <t>low</t>
@@ -1330,7 +1330,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>2026-06-29T11:52:24.359840+00:00</t>
+    <t>2026-07-06T11:21:17.594987+00:00</t>
   </si>
   <si>
     <t>synthetic scenario: base</t>

--- a/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
+++ b/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at UTC</t>
   </si>
   <si>
-    <t>2026-07-06T11:21:23.872004+00:00</t>
+    <t>2026-07-13T10:15:32.124430+00:00</t>
   </si>
   <si>
     <t>Data status</t>
@@ -598,151 +598,151 @@
     <t>suggested_action</t>
   </si>
   <si>
-    <t>2026-07-06 11:21:22.153256+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.184848+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.208285+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.240237+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.269272+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.293515+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.311356+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.337088+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.356460+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.376906+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.400081+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.425359+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.444587+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.469014+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.486900+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.505041+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.520839+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.538886+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.562744+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.587107+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.604201+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.617188+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.631591+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.690560+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.751358+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.779791+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.801858+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.833488+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.860255+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.884933+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.903501+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.929657+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.948082+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.968819+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:22.992454+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:23.018078+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:23.037846+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:23.062602+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:23.080502+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:23.098605+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:23.114728+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:23.132944+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:23.157194+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:23.181475+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:23.198656+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:23.211910+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:23.225249+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:23.242871+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:21:23.368389+00:00</t>
+    <t>2026-07-13 10:15:30.262315+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.296917+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.327225+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.364722+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.394778+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.421435+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.441350+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.469511+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.489398+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.512096+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.537441+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.565394+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.587022+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.614018+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.633975+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.654215+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.672106+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.692097+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.718888+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.746093+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.765151+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.779666+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.794334+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.814144+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.871831+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.901872+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.926413+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:30.982628+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:31.012371+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:31.039734+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:31.059956+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:31.088474+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:31.108891+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:31.131705+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:31.157497+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:31.185911+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:31.207610+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:31.235046+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:31.255316+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:31.275700+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:31.293376+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:31.313831+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:31.340771+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:31.367794+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:31.386901+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:31.401928+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:31.416808+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:31.436583+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:15:31.584494+00:00</t>
   </si>
   <si>
     <t>low</t>
@@ -1330,7 +1330,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>2026-07-06T11:21:17.594987+00:00</t>
+    <t>2026-07-13T10:15:25.311178+00:00</t>
   </si>
   <si>
     <t>synthetic scenario: base</t>

--- a/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
+++ b/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at UTC</t>
   </si>
   <si>
-    <t>2026-07-13T10:15:32.124430+00:00</t>
+    <t>2026-07-20T09:49:13.121613+00:00</t>
   </si>
   <si>
     <t>Data status</t>
@@ -598,151 +598,151 @@
     <t>suggested_action</t>
   </si>
   <si>
-    <t>2026-07-13 10:15:30.262315+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.296917+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.327225+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.364722+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.394778+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.421435+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.441350+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.469511+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.489398+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.512096+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.537441+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.565394+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.587022+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.614018+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.633975+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.654215+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.672106+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.692097+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.718888+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.746093+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.765151+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.779666+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.794334+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.814144+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.871831+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.901872+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.926413+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:30.982628+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:31.012371+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:31.039734+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:31.059956+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:31.088474+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:31.108891+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:31.131705+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:31.157497+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:31.185911+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:31.207610+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:31.235046+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:31.255316+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:31.275700+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:31.293376+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:31.313831+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:31.340771+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:31.367794+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:31.386901+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:31.401928+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:31.416808+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:31.436583+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:15:31.584494+00:00</t>
+    <t>2026-07-20 09:49:11.448329+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:11.477968+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:11.500727+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:11.533925+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:11.562260+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:11.586995+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:11.605612+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:11.631435+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:11.649596+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:11.670065+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:11.693672+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:11.719239+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:11.738769+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:11.763611+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:11.781838+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:11.800225+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:11.816232+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:11.834472+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:11.858770+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:11.883397+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:11.900612+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:11.913797+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:11.927057+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:11.945175+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:11.995809+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:12.022913+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:12.045409+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:12.096110+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:12.123321+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:12.147849+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:12.165822+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:12.192141+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:12.210777+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:12.231558+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:12.254932+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:12.280969+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:12.300626+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:12.325415+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:12.343396+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:12.362061+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:12.378075+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:12.396367+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:12.420566+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:12.444996+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:12.462226+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:12.475501+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:12.488721+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:12.506323+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-20 09:49:12.631310+00:00</t>
   </si>
   <si>
     <t>low</t>
@@ -1330,7 +1330,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>2026-07-13T10:15:25.311178+00:00</t>
+    <t>2026-07-20T09:49:06.781899+00:00</t>
   </si>
   <si>
     <t>synthetic scenario: base</t>

--- a/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
+++ b/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at UTC</t>
   </si>
   <si>
-    <t>2026-07-20T09:49:13.121613+00:00</t>
+    <t>2026-07-27T10:31:33.492858+00:00</t>
   </si>
   <si>
     <t>Data status</t>
@@ -598,151 +598,151 @@
     <t>suggested_action</t>
   </si>
   <si>
-    <t>2026-07-20 09:49:11.448329+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:11.477968+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:11.500727+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:11.533925+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:11.562260+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:11.586995+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:11.605612+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:11.631435+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:11.649596+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:11.670065+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:11.693672+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:11.719239+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:11.738769+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:11.763611+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:11.781838+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:11.800225+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:11.816232+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:11.834472+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:11.858770+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:11.883397+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:11.900612+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:11.913797+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:11.927057+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:11.945175+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:11.995809+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:12.022913+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:12.045409+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:12.096110+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:12.123321+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:12.147849+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:12.165822+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:12.192141+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:12.210777+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:12.231558+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:12.254932+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:12.280969+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:12.300626+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:12.325415+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:12.343396+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:12.362061+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:12.378075+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:12.396367+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:12.420566+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:12.444996+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:12.462226+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:12.475501+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:12.488721+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:12.506323+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-20 09:49:12.631310+00:00</t>
+    <t>2026-07-27 10:31:31.808906+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:31.840030+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:31.863308+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:31.896754+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:31.924793+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:31.950129+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:31.968098+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:31.994250+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.012947+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.033797+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.057525+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.083143+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.102854+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.128329+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.146494+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.165078+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.181070+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.199342+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.223665+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.248372+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.265749+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.278902+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.292240+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.310184+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.360836+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.388323+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.431538+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.463391+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.490237+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.514786+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.532768+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.558743+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.577290+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.598222+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.622156+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.648069+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.668072+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.693214+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.711414+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.729980+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.746058+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.764570+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.788990+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.813857+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.831504+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.845037+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.858655+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:32.876675+00:00</t>
+  </si>
+  <si>
+    <t>2026-07-27 10:31:33.001571+00:00</t>
   </si>
   <si>
     <t>low</t>
@@ -1330,7 +1330,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>2026-07-20T09:49:06.781899+00:00</t>
+    <t>2026-07-27T10:31:27.325411+00:00</t>
   </si>
   <si>
     <t>synthetic scenario: base</t>

--- a/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
+++ b/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at UTC</t>
   </si>
   <si>
-    <t>2026-07-27T10:31:33.492858+00:00</t>
+    <t>2026-08-03T10:31:51.814405+00:00</t>
   </si>
   <si>
     <t>Data status</t>
@@ -598,151 +598,151 @@
     <t>suggested_action</t>
   </si>
   <si>
-    <t>2026-07-27 10:31:31.808906+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:31.840030+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:31.863308+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:31.896754+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:31.924793+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:31.950129+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:31.968098+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:31.994250+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.012947+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.033797+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.057525+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.083143+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.102854+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.128329+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.146494+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.165078+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.181070+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.199342+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.223665+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.248372+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.265749+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.278902+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.292240+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.310184+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.360836+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.388323+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.431538+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.463391+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.490237+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.514786+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.532768+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.558743+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.577290+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.598222+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.622156+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.648069+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.668072+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.693214+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.711414+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.729980+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.746058+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.764570+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.788990+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.813857+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.831504+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.845037+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.858655+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:32.876675+00:00</t>
-  </si>
-  <si>
-    <t>2026-07-27 10:31:33.001571+00:00</t>
+    <t>2026-08-03 10:31:50.016513+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.050187+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.077267+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.113262+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.143770+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.171075+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.190765+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.219076+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.239292+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.261874+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.287667+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.315678+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.337188+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.364495+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.384873+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.405394+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.422992+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.443025+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.469466+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.496747+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.515738+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.530477+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.545167+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.565164+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.621285+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.651180+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.693700+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.728514+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.758023+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.785485+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.805098+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.833502+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.853643+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.876452+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.902425+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.930480+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.952068+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.979300+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:50.999279+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:51.019720+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:51.037405+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:51.057733+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:51.084704+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:51.111793+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:51.130945+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:51.145648+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:51.160303+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:51.180059+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 10:31:51.322477+00:00</t>
   </si>
   <si>
     <t>low</t>
@@ -1330,7 +1330,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>2026-07-27T10:31:27.325411+00:00</t>
+    <t>2026-08-03T10:31:45.283210+00:00</t>
   </si>
   <si>
     <t>synthetic scenario: base</t>

--- a/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
+++ b/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at UTC</t>
   </si>
   <si>
-    <t>2026-08-03T10:31:51.814405+00:00</t>
+    <t>2026-08-10T08:20:29.135318+00:00</t>
   </si>
   <si>
     <t>Data status</t>
@@ -598,151 +598,151 @@
     <t>suggested_action</t>
   </si>
   <si>
-    <t>2026-08-03 10:31:50.016513+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.050187+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.077267+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.113262+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.143770+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.171075+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.190765+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.219076+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.239292+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.261874+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.287667+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.315678+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.337188+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.364495+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.384873+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.405394+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.422992+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.443025+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.469466+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.496747+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.515738+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.530477+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.545167+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.565164+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.621285+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.651180+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.693700+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.728514+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.758023+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.785485+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.805098+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.833502+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.853643+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.876452+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.902425+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.930480+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.952068+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.979300+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:50.999279+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:51.019720+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:51.037405+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:51.057733+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:51.084704+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:51.111793+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:51.130945+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:51.145648+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:51.160303+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:51.180059+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 10:31:51.322477+00:00</t>
+    <t>2026-08-10 08:20:27.328445+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:27.362455+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:27.388589+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:27.423829+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:27.455679+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:27.482952+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:27.502793+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:27.531383+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:27.551647+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:27.574338+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:27.600070+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:27.628071+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:27.649603+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:27.676594+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:27.696679+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:27.717572+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:27.735323+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:27.755557+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:27.782449+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:27.809910+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:27.829052+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:27.843711+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:27.858572+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:27.878571+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:27.935202+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:27.965045+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:28.008835+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:28.044385+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:28.074400+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:28.101512+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:28.121465+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:28.150047+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:28.170777+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:28.194348+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:28.221056+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:28.249201+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:28.270715+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:28.298064+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:28.317834+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:28.337930+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:28.355613+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:28.375736+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:28.402442+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:28.429534+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:28.448579+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:28.463288+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:28.477989+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:28.497783+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-10 08:20:28.639058+00:00</t>
   </si>
   <si>
     <t>low</t>
@@ -1330,7 +1330,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>2026-08-03T10:31:45.283210+00:00</t>
+    <t>2026-08-10T08:20:22.539048+00:00</t>
   </si>
   <si>
     <t>synthetic scenario: base</t>

--- a/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
+++ b/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at UTC</t>
   </si>
   <si>
-    <t>2026-08-10T08:20:29.135318+00:00</t>
+    <t>2026-08-17T07:42:27.946823+00:00</t>
   </si>
   <si>
     <t>Data status</t>
@@ -598,151 +598,151 @@
     <t>suggested_action</t>
   </si>
   <si>
-    <t>2026-08-10 08:20:27.328445+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:27.362455+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:27.388589+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:27.423829+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:27.455679+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:27.482952+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:27.502793+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:27.531383+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:27.551647+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:27.574338+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:27.600070+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:27.628071+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:27.649603+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:27.676594+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:27.696679+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:27.717572+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:27.735323+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:27.755557+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:27.782449+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:27.809910+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:27.829052+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:27.843711+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:27.858572+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:27.878571+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:27.935202+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:27.965045+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:28.008835+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:28.044385+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:28.074400+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:28.101512+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:28.121465+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:28.150047+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:28.170777+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:28.194348+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:28.221056+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:28.249201+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:28.270715+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:28.298064+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:28.317834+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:28.337930+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:28.355613+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:28.375736+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:28.402442+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:28.429534+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:28.448579+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:28.463288+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:28.477989+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:28.497783+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-10 08:20:28.639058+00:00</t>
+    <t>2026-08-17 07:42:26.003154+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.039285+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.066009+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.104250+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.137428+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.165065+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.185846+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.215520+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.236702+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.260399+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.287129+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.315836+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.338139+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.366001+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.386759+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.407527+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.425689+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.446388+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.473674+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.501531+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.521111+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.536076+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.551345+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.571681+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.630322+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.687400+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.712683+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.749185+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.780404+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.808043+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.828400+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.857499+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.878345+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.902182+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.928630+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.957582+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:26.979979+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:27.008245+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:27.029037+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:27.049936+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:27.068219+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:27.089242+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:27.116939+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:27.144850+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:27.168900+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:27.184024+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:27.199147+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:27.219247+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 07:42:27.368922+00:00</t>
   </si>
   <si>
     <t>low</t>
@@ -1330,7 +1330,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>2026-08-10T08:20:22.539048+00:00</t>
+    <t>2026-08-17T07:42:20.731548+00:00</t>
   </si>
   <si>
     <t>synthetic scenario: base</t>

--- a/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
+++ b/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at UTC</t>
   </si>
   <si>
-    <t>2026-08-17T07:42:27.946823+00:00</t>
+    <t>2026-08-24T07:48:49.681142+00:00</t>
   </si>
   <si>
     <t>Data status</t>
@@ -598,151 +598,151 @@
     <t>suggested_action</t>
   </si>
   <si>
-    <t>2026-08-17 07:42:26.003154+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.039285+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.066009+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.104250+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.137428+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.165065+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.185846+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.215520+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.236702+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.260399+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.287129+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.315836+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.338139+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.366001+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.386759+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.407527+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.425689+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.446388+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.473674+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.501531+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.521111+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.536076+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.551345+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.571681+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.630322+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.687400+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.712683+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.749185+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.780404+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.808043+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.828400+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.857499+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.878345+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.902182+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.928630+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.957582+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:26.979979+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:27.008245+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:27.029037+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:27.049936+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:27.068219+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:27.089242+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:27.116939+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:27.144850+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:27.168900+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:27.184024+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:27.199147+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:27.219247+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-17 07:42:27.368922+00:00</t>
+    <t>2026-08-24 07:48:48.300956+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.325533+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.343995+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.370130+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.397791+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.417439+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.431707+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.452248+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.466907+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.483469+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.502301+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.522512+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.538266+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.558000+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.572405+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.586856+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.599537+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.613993+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.633141+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.652717+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.666434+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.676748+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.687331+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.701882+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.743032+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.792544+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.810263+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.835414+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.857000+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.876471+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.890659+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.911541+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.926245+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.942988+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.961792+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.982288+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:48.998126+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:49.017944+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:49.032582+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:49.047186+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:49.059850+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:49.074473+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:49.093927+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:49.113598+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:49.127532+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:49.138229+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:49.148868+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:49.162989+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-24 07:48:49.262896+00:00</t>
   </si>
   <si>
     <t>low</t>
@@ -1330,7 +1330,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>2026-08-17T07:42:20.731548+00:00</t>
+    <t>2026-08-24T07:48:44.384563+00:00</t>
   </si>
   <si>
     <t>synthetic scenario: base</t>

--- a/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
+++ b/frontend/public/reports/ev_flex_daily_trading_report_sample.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at UTC</t>
   </si>
   <si>
-    <t>2026-08-24T07:48:49.681142+00:00</t>
+    <t>2026-08-31T14:33:08.054698+00:00</t>
   </si>
   <si>
     <t>Data status</t>
@@ -598,151 +598,151 @@
     <t>suggested_action</t>
   </si>
   <si>
-    <t>2026-08-24 07:48:48.300956+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.325533+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.343995+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.370130+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.397791+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.417439+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.431707+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.452248+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.466907+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.483469+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.502301+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.522512+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.538266+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.558000+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.572405+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.586856+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.599537+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.613993+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.633141+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.652717+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.666434+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.676748+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.687331+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.701882+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.743032+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.792544+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.810263+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.835414+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.857000+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.876471+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.890659+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.911541+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.926245+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.942988+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.961792+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.982288+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:48.998126+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:49.017944+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:49.032582+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:49.047186+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:49.059850+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:49.074473+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:49.093927+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:49.113598+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:49.127532+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:49.138229+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:49.148868+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:49.162989+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-24 07:48:49.262896+00:00</t>
+    <t>2026-08-31 14:33:06.251101+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.281591+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.305101+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.338617+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.369373+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.394536+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.413569+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.440459+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.459630+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.481219+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.505419+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.531867+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.552440+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.577921+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.596703+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.615743+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.632319+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.651255+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.676173+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.701457+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.719376+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.732804+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.746638+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.765007+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.817752+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.878504+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.901414+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.934066+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.961739+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:06.986898+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:07.005564+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:07.032351+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:07.051491+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:07.073137+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:07.097518+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:07.123932+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:07.144175+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:07.169969+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:07.188778+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:07.207735+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:07.224391+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:07.243226+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:07.268385+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:07.293986+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:07.311675+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:07.325288+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:07.338957+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:07.357447+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 14:33:07.489763+00:00</t>
   </si>
   <si>
     <t>low</t>
@@ -1330,7 +1330,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>2026-08-24T07:48:44.384563+00:00</t>
+    <t>2026-08-31T14:33:01.574773+00:00</t>
   </si>
   <si>
     <t>synthetic scenario: base</t>
